--- a/data/trans_dic/IP22_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 19,6</t>
+          <t>7,93; 19,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,24; 30,81</t>
+          <t>15,9; 30,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,9; 27,34</t>
+          <t>9,97; 27,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 48,44</t>
+          <t>6,67; 46,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 22,6</t>
+          <t>9,88; 22,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,05; 39,95</t>
+          <t>23,49; 40,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 18,97</t>
+          <t>5,97; 18,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 29,67</t>
+          <t>10,45; 29,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 18,85</t>
+          <t>10,52; 18,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 32,37</t>
+          <t>21,96; 33,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 20,11</t>
+          <t>10,28; 19,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 31,8</t>
+          <t>11,65; 31,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 24,29</t>
+          <t>18,15; 24,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,92; 26,55</t>
+          <t>19,96; 26,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 19,97</t>
+          <t>14,36; 20,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,95</t>
+          <t>10,66; 16,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 25,03</t>
+          <t>19,1; 24,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,72; 31,62</t>
+          <t>24,84; 31,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 19,7</t>
+          <t>14,4; 20,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 17,23</t>
+          <t>11,29; 17,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 24,06</t>
+          <t>19,06; 23,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 28,17</t>
+          <t>23,24; 28,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,03; 18,93</t>
+          <t>15,13; 18,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,12</t>
+          <t>11,92; 16,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,96</t>
+          <t>13,96; 23,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,67; 30,69</t>
+          <t>19,4; 30,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 24,79</t>
+          <t>14,66; 24,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 25,59</t>
+          <t>15,32; 26,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,23; 31,0</t>
+          <t>19,97; 31,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,43; 29,72</t>
+          <t>19,6; 30,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 23,31</t>
+          <t>13,9; 23,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 23,14</t>
+          <t>12,74; 23,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 25,33</t>
+          <t>18,56; 25,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,02; 29,17</t>
+          <t>21,15; 28,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 22,52</t>
+          <t>15,55; 22,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,06; 22,53</t>
+          <t>15,14; 22,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,77</t>
+          <t>16,86; 21,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,33</t>
+          <t>20,83; 26,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 20,33</t>
+          <t>15,42; 19,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,92</t>
+          <t>12,85; 19,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,42; 24,5</t>
+          <t>19,39; 24,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,96; 30,29</t>
+          <t>24,57; 30,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,17</t>
+          <t>14,55; 19,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,11</t>
+          <t>13,07; 17,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 22,19</t>
+          <t>18,91; 22,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 27,66</t>
+          <t>24,01; 27,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,87</t>
+          <t>15,48; 18,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 17,77</t>
+          <t>13,53; 17,58</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7308; 17814</t>
+          <t>7208; 18110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14997; 28462</t>
+          <t>14683; 27940</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6472; 16236</t>
+          <t>5919; 16101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3957; 26488</t>
+          <t>3646; 25420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8210; 19623</t>
+          <t>8580; 19579</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19670; 34094</t>
+          <t>20044; 34259</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4432; 13018</t>
+          <t>4099; 12945</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6568; 18397</t>
+          <t>6481; 18456</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18458; 33505</t>
+          <t>18698; 33379</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37811; 57515</t>
+          <t>39024; 58657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12478; 25742</t>
+          <t>13157; 25566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13299; 37105</t>
+          <t>13595; 37221</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74957; 101072</t>
+          <t>75521; 102291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89971; 119906</t>
+          <t>90116; 120776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67755; 94294</t>
+          <t>67844; 95254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49576; 77803</t>
+          <t>48939; 77045</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89824; 119371</t>
+          <t>91108; 118172</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121651; 155614</t>
+          <t>122265; 155131</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68959; 96280</t>
+          <t>70381; 98279</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58717; 89012</t>
+          <t>58320; 89869</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>172147; 214916</t>
+          <t>170206; 210192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>220070; 265884</t>
+          <t>219341; 264791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>144478; 181942</t>
+          <t>145418; 182428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>116270; 157223</t>
+          <t>116280; 158421</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24914; 41707</t>
+          <t>24308; 41614</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32812; 51190</t>
+          <t>32365; 51284</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26144; 42807</t>
+          <t>25322; 41992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21373; 38267</t>
+          <t>22913; 39636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31986; 49017</t>
+          <t>31578; 49134</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33464; 51182</t>
+          <t>33760; 52256</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25537; 43523</t>
+          <t>25944; 43163</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23229; 42427</t>
+          <t>23358; 43505</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59701; 84157</t>
+          <t>61669; 85505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71252; 98913</t>
+          <t>71700; 97399</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56524; 80935</t>
+          <t>55871; 80435</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50125; 75013</t>
+          <t>50415; 75067</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114820; 148284</t>
+          <t>114811; 148370</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149607; 187162</t>
+          <t>148063; 187006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109625; 143203</t>
+          <t>108595; 140126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85684; 125508</t>
+          <t>85213; 126818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>140230; 176869</t>
+          <t>139964; 176140</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>187134; 227102</t>
+          <t>184231; 227548</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108303; 142659</t>
+          <t>108277; 141691</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99644; 138030</t>
+          <t>99617; 135313</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>264501; 311355</t>
+          <t>265351; 317361</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>347667; 403890</t>
+          <t>350714; 403797</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>227897; 273282</t>
+          <t>224244; 271598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>194441; 253286</t>
+          <t>192871; 250613</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP22_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22,86%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17,32%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 19,93</t>
+          <t>10,07; 22,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,9; 30,25</t>
+          <t>23,28; 40,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 27,12</t>
+          <t>6,17; 19,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 46,49</t>
+          <t>10,11; 29,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 22,55</t>
+          <t>8,75; 20,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,49; 40,15</t>
+          <t>15,86; 30,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 18,87</t>
+          <t>10,5; 27,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 29,77</t>
+          <t>6,25; 21,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 18,78</t>
+          <t>10,34; 19,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,96; 33,01</t>
+          <t>21,24; 32,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,97</t>
+          <t>10,22; 20,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,65; 31,9</t>
+          <t>9,75; 23,2</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>20,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>16,96%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 24,58</t>
+          <t>19,01; 25,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 26,75</t>
+          <t>24,4; 31,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 20,17</t>
+          <t>14,21; 20,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 16,79</t>
+          <t>11,32; 17,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 24,77</t>
+          <t>18,21; 24,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 31,52</t>
+          <t>19,98; 26,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 20,11</t>
+          <t>14,19; 19,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 17,4</t>
+          <t>11,15; 16,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,06; 23,54</t>
+          <t>19,07; 23,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,24; 28,06</t>
+          <t>23,41; 28,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 18,98</t>
+          <t>15,08; 19,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,24</t>
+          <t>11,84; 16,04</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24,57%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24,97%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,22%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 23,91</t>
+          <t>20,07; 31,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 30,74</t>
+          <t>19,2; 30,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 24,31</t>
+          <t>13,98; 23,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 26,5</t>
+          <t>12,44; 23,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,97; 31,07</t>
+          <t>14,48; 24,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 30,34</t>
+          <t>19,87; 30,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 23,12</t>
+          <t>15,11; 24,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 23,73</t>
+          <t>15,18; 25,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,56; 25,74</t>
+          <t>18,45; 25,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,15; 28,73</t>
+          <t>20,99; 29,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,55; 22,38</t>
+          <t>15,28; 21,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 22,55</t>
+          <t>15,08; 22,64</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,79</t>
+          <t>19,34; 24,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,83; 26,31</t>
+          <t>24,92; 30,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,42; 19,89</t>
+          <t>14,51; 19,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 19,12</t>
+          <t>12,93; 17,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,39; 24,4</t>
+          <t>17,06; 21,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,57; 30,35</t>
+          <t>21,26; 26,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,04</t>
+          <t>15,45; 19,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,76</t>
+          <t>12,89; 17,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 22,62</t>
+          <t>18,68; 22,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,01; 27,65</t>
+          <t>23,69; 27,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 18,75</t>
+          <t>15,63; 18,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 17,58</t>
+          <t>13,36; 17,02</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26828</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8067</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9793</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12081</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>21111</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>10284</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10660</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26828</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8067</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>15577</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7208; 18110</t>
+          <t>8741; 19820</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14683; 27940</t>
+          <t>19868; 34511</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5919; 16101</t>
+          <t>4231; 13168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3646; 25420</t>
+          <t>5736; 16524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8580; 19579</t>
+          <t>7952; 18602</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20044; 34259</t>
+          <t>14654; 27795</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4099; 12945</t>
+          <t>6233; 16133</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6481; 18456</t>
+          <t>2923; 10012</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18698; 33379</t>
+          <t>18381; 34155</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39024; 58657</t>
+          <t>37750; 58436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13157; 25566</t>
+          <t>13076; 25763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13595; 37221</t>
+          <t>10086; 24012</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103582</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>137670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82341</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66973</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>87082</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>105050</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>80078</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62926</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>103582</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>137670</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82341</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>73221</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>136147</t>
+          <t>127018</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75521; 102291</t>
+          <t>90665; 119835</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90116; 120776</t>
+          <t>120088; 154766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67844; 95254</t>
+          <t>69452; 97967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48939; 77045</t>
+          <t>53849; 82600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91108; 118172</t>
+          <t>75789; 101120</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122265; 155131</t>
+          <t>90227; 120700</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70381; 98279</t>
+          <t>67032; 93290</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58320; 89869</t>
+          <t>48065; 72504</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>170206; 210192</t>
+          <t>170297; 210187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>219341; 264791</t>
+          <t>220936; 264765</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145418; 182428</t>
+          <t>144934; 184693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>116280; 158421</t>
+          <t>107331; 145392</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39888</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42320</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34120</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28856</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>32498</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>41657</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>33722</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29649</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>39888</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42320</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34120</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>58814</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24308; 41614</t>
+          <t>31735; 49134</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32365; 51284</t>
+          <t>33068; 52747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25322; 41992</t>
+          <t>26089; 43711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22913; 39636</t>
+          <t>20952; 39242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31578; 49134</t>
+          <t>25199; 42364</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33760; 52256</t>
+          <t>33139; 51414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25944; 43163</t>
+          <t>26092; 42374</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23358; 43505</t>
+          <t>22761; 38904</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61669; 85505</t>
+          <t>61277; 85632</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71700; 97399</t>
+          <t>71178; 99003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55871; 80435</t>
+          <t>54914; 78801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50415; 75067</t>
+          <t>48014; 72100</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95787</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114811; 148370</t>
+          <t>139634; 174556</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148063; 187006</t>
+          <t>186823; 227905</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>108595; 140126</t>
+          <t>107955; 142338</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85213; 126818</t>
+          <t>90588; 125160</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>139964; 176140</t>
+          <t>116201; 149172</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>184231; 227548</t>
+          <t>151095; 186466</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108277; 141691</t>
+          <t>108859; 140183</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>99617; 135313</t>
+          <t>80897; 111000</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>265351; 317361</t>
+          <t>262134; 313339</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>350714; 403797</t>
+          <t>345936; 401907</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>224244; 271598</t>
+          <t>226452; 272633</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>192871; 250613</t>
+          <t>177422; 226078</t>
         </is>
       </c>
     </row>
